--- a/product_selector_out/STM32 Arm Cortex MPUs.xlsx
+++ b/product_selector_out/STM32 Arm Cortex MPUs.xlsx
@@ -1744,7 +1744,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp131a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp131c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="BC18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp133a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="BC19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp133c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="BC22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp135a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="BC23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp135c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="BC26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp151a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="BC27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp151c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="BC30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp153a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="BC31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp153c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="BC34" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp157a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="BC35" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp157c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BC38" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="BC39" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="BC40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="BC41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="BC42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9777,7 +9777,7 @@
       </c>
       <c r="BC43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="BC44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="BC45" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="BC46" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="BC47" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="BC50" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="BC51" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="BC52" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="BC53" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="BC54" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="BC55" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="BC56" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13655,7 +13655,7 @@
       </c>
       <c r="BC57" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="BC58" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="BC59" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="BC62" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="BC63" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="BC64" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="BC65" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="BC66" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="BC67" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="BC68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="BC69" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17256,7 +17256,7 @@
       </c>
       <c r="BC70" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="BC71" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="BC72" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18087,7 +18087,7 @@
       </c>
       <c r="BC73" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18364,7 +18364,7 @@
       </c>
       <c r="BC74" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="BC75" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19778,9 +19778,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -20028,9 +20028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20055,9 +20055,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -20305,9 +20305,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20886,9 +20886,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -21136,9 +21136,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21163,9 +21163,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -21413,9 +21413,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21994,9 +21994,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -22244,9 +22244,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22271,9 +22271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -22521,9 +22521,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -23102,9 +23102,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -23252,14 +23252,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK26" s="6" t="inlineStr">
@@ -23352,9 +23352,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -23379,9 +23379,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -23529,14 +23529,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK27" s="6" t="inlineStr">
@@ -23629,9 +23629,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -24210,9 +24210,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -24360,14 +24360,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK30" s="6" t="inlineStr">
@@ -24460,9 +24460,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -24487,9 +24487,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -24637,14 +24637,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK31" s="6" t="inlineStr">
@@ -24737,9 +24737,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -25318,9 +25318,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -25468,14 +25468,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK34" s="6" t="inlineStr">
@@ -25568,9 +25568,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -25595,9 +25595,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -25745,14 +25745,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK35" s="6" t="inlineStr">
@@ -25845,9 +25845,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -26421,14 +26421,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -26576,14 +26576,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK38" s="6" t="inlineStr">
@@ -26676,9 +26676,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -26698,14 +26698,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -26853,14 +26853,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK39" s="6" t="inlineStr">
@@ -26953,9 +26953,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -26975,14 +26975,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -27130,14 +27130,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK40" s="6" t="inlineStr">
@@ -27230,9 +27230,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -27252,14 +27252,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -27407,14 +27407,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK41" s="6" t="inlineStr">
@@ -27507,9 +27507,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -27529,14 +27529,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -27684,14 +27684,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK42" s="6" t="inlineStr">
@@ -27784,9 +27784,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -27806,14 +27806,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -27961,14 +27961,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK43" s="6" t="inlineStr">
@@ -28061,9 +28061,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -28083,14 +28083,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -28238,14 +28238,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK44" s="6" t="inlineStr">
@@ -28338,9 +28338,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -28360,14 +28360,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -28515,14 +28515,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK45" s="6" t="inlineStr">
@@ -28615,9 +28615,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -28637,14 +28637,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -28792,14 +28792,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK46" s="6" t="inlineStr">
@@ -28892,9 +28892,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BC46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -28914,14 +28914,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -29069,14 +29069,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI47" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ47" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK47" s="6" t="inlineStr">
@@ -29169,9 +29169,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -29750,9 +29750,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -29900,14 +29900,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI50" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ50" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK50" s="6" t="inlineStr">
@@ -30000,9 +30000,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -30027,9 +30027,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -30177,14 +30177,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI51" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ51" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI51" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ51" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK51" s="6" t="inlineStr">
@@ -30277,9 +30277,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -30304,9 +30304,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -30454,14 +30454,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI52" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ52" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK52" s="6" t="inlineStr">
@@ -30554,9 +30554,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -30581,9 +30581,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -30731,14 +30731,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI53" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ53" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK53" s="6" t="inlineStr">
@@ -30831,9 +30831,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -30858,9 +30858,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -31008,14 +31008,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK54" s="6" t="inlineStr">
@@ -31108,9 +31108,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -31135,9 +31135,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -31285,14 +31285,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI55" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ55" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK55" s="6" t="inlineStr">
@@ -31385,9 +31385,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -31412,9 +31412,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -31562,14 +31562,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI56" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ56" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK56" s="6" t="inlineStr">
@@ -31662,9 +31662,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -31689,9 +31689,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -31839,14 +31839,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK57" s="6" t="inlineStr">
@@ -31939,9 +31939,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -31966,9 +31966,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -32116,14 +32116,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK58" s="6" t="inlineStr">
@@ -32216,9 +32216,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -32243,9 +32243,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -32393,14 +32393,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AJ59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK59" s="6" t="inlineStr">
@@ -32493,9 +32493,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -33074,9 +33074,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -33224,14 +33224,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK62" s="6" t="inlineStr">
@@ -33324,9 +33324,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -33351,9 +33351,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -33501,14 +33501,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI63" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ63" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK63" s="6" t="inlineStr">
@@ -33601,9 +33601,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC63" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -33628,9 +33628,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -33778,14 +33778,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK64" s="6" t="inlineStr">
@@ -33878,9 +33878,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -33905,9 +33905,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -34055,14 +34055,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK65" s="6" t="inlineStr">
@@ -34155,9 +34155,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -34182,9 +34182,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -34332,14 +34332,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK66" s="6" t="inlineStr">
@@ -34432,9 +34432,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC66" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -34459,9 +34459,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -34609,14 +34609,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK67" s="6" t="inlineStr">
@@ -34709,9 +34709,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -34736,9 +34736,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -34886,14 +34886,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK68" s="6" t="inlineStr">
@@ -34986,9 +34986,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -35013,9 +35013,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -35163,14 +35163,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK69" s="6" t="inlineStr">
@@ -35263,9 +35263,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -35290,9 +35290,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -35440,14 +35440,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK70" s="6" t="inlineStr">
@@ -35540,9 +35540,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -35567,9 +35567,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -35717,14 +35717,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK71" s="6" t="inlineStr">
@@ -35817,9 +35817,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -35844,9 +35844,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -35994,14 +35994,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK72" s="6" t="inlineStr">
@@ -36094,9 +36094,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36121,9 +36121,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -36271,14 +36271,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK73" s="6" t="inlineStr">
@@ -36371,9 +36371,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36398,9 +36398,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -36548,14 +36548,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK74" s="6" t="inlineStr">
@@ -36648,9 +36648,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36675,9 +36675,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -36825,14 +36825,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI75" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AJ75" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK75" s="6" t="inlineStr">
@@ -36925,9 +36925,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36946,7 +36946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37112,7 +37112,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32MP151D</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -37134,7 +37134,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32MP151D</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -37156,7 +37156,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32MP151D</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -37178,7 +37178,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32MP151F</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -37200,7 +37200,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32MP151F</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -37222,7 +37222,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32MP151F</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -37244,7 +37244,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP157A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -37266,7 +37266,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP157A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -37288,7 +37288,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP157A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -37310,7 +37310,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP157C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -37332,7 +37332,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP157C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -37354,7 +37354,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP157C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -37376,12 +37376,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32MP153D</t>
+          <t>STM32MP211A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -37391,19 +37391,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32MP153D</t>
+          <t>STM32MP211A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -37413,19 +37413,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32MP153D</t>
+          <t>STM32MP211A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -37435,19 +37435,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32MP153F</t>
+          <t>STM32MP211A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -37457,19 +37457,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32MP153F</t>
+          <t>STM32MP211C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -37479,19 +37479,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32MP153F</t>
+          <t>STM32MP211C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -37501,19 +37501,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32MP157A</t>
+          <t>STM32MP211C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -37523,19 +37523,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32MP157A</t>
+          <t>STM32MP211C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -37545,19 +37545,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32MP157A</t>
+          <t>STM32MP231A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -37567,19 +37567,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32MP157C</t>
+          <t>STM32MP231A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -37589,19 +37589,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32MP157C</t>
+          <t>STM32MP231A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -37611,19 +37611,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32MP157C</t>
+          <t>STM32MP231C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -37633,19 +37633,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32MP157D</t>
+          <t>STM32MP231C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -37655,19 +37655,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32MP157D</t>
+          <t>STM32MP231C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -37677,19 +37677,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32MP157D</t>
+          <t>STM32MP251A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -37699,19 +37699,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32MP157F</t>
+          <t>STM32MP251A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -37721,19 +37721,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32MP157F</t>
+          <t>STM32MP251A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -37743,19 +37743,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32MP157F</t>
+          <t>STM32MP251C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -37765,19 +37765,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP251C</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -37787,19 +37787,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP251C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -37808,2866 +37808,6 @@
         </is>
       </c>
       <c r="D39" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32MP211A</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32MP211A</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32MP211C</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32MP211C</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32MP211C</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32MP211C</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32MP211D</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32MP211D</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32MP211D</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32MP211D</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32MP211F</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32MP211F</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32MP211F</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32MP211F</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32MP213A</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32MP213A</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32MP213A</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32MP213A</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32MP213C</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32MP213C</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32MP213C</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32MP213C</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32MP213D</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32MP213D</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32MP213D</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32MP213D</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32MP213F</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>STM32MP213F</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>STM32MP213F</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>STM32MP213F</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>STM32MP215A</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>STM32MP215A</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32MP215A</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32MP215A</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STM32MP215C</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>STM32MP215C</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32MP215C</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32MP215C</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32MP215D</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>STM32MP215D</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>STM32MP215D</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STM32MP215D</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>STM32MP215F</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>STM32MP215F</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>STM32MP215F</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STM32MP215F</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32MP231A</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32MP231A</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32MP231A</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STM32MP231C</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>STM32MP231C</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STM32MP231C</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>STM32MP231D</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32MP231D</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32MP231D</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32MP231F</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32MP231F</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32MP231F</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>STM32MP233A</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STM32MP233A</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>STM32MP233A</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>STM32MP233C</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>STM32MP233C</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32MP233C</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>STM32MP233D</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>STM32MP233D</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>STM32MP233D</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>STM32MP233F</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>STM32MP233F</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>STM32MP233F</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>STM32MP235A</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>STM32MP235A</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>STM32MP235A</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>STM32MP235C</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>STM32MP235C</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>STM32MP235C</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STM32MP235D</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>STM32MP235D</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM32MP235D</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM32MP235F</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32MP235F</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM32MP235F</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>STM32MP251A</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM32MP251A</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM32MP251A</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM32MP251C</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM32MP251C</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM32MP251C</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM32MP251D</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM32MP251D</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32MP251D</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32MP251F</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32MP251F</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32MP251F</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM32MP253A</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM32MP253A</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM32MP253A</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM32MP253C</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>STM32MP253C</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STM32MP253C</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>STM32MP253D</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>STM32MP253D</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>STM32MP253D</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>STM32MP253F</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>STM32MP253F</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>STM32MP253F</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>STM32MP255A</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>STM32MP255A</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>STM32MP255A</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>STM32MP255C</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>STM32MP255C</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>STM32MP255C</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>STM32MP255D</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>STM32MP255D</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>STM32MP255D</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>STM32MP255F</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>STM32MP255F</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>STM32MP255F</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>STM32MP257A</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>STM32MP257A</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>STM32MP257A</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>STM32MP257C</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>STM32MP257C</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>STM32MP257C</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>STM32MP257D</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>STM32MP257D</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>STM32MP257D</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>STM32MP257F</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>STM32MP257F</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>STM32MP257F</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
         <is>
           <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32 Arm Cortex MPUs.xlsx
+++ b/product_selector_out/STM32 Arm Cortex MPUs.xlsx
@@ -1744,7 +1744,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp131a.pdf</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp131c.pdf</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="BC18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp133a.pdf</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="BC19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp133c.pdf</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="BC22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp135a.pdf</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="BC23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp135c.pdf</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="BC26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp151a.pdf</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="BC27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp151c.pdf</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="BC30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp153a.pdf</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="BC31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp153c.pdf</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="BC34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp157a.pdf</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="BC35" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp157c.pdf</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BC38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="BC39" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="BC40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="BC41" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="BC42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -9777,7 +9777,7 @@
       </c>
       <c r="BC43" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="BC44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="BC45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="BC46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="BC47" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="BC50" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="BC51" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="BC52" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="BC53" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="BC54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="BC55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="BC56" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -13655,7 +13655,7 @@
       </c>
       <c r="BC57" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="BC58" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="BC59" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="BC62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="BC63" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="BC64" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="BC65" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="BC66" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="BC67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="BC68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="BC69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -17256,7 +17256,7 @@
       </c>
       <c r="BC70" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="BC71" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="BC72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -18087,7 +18087,7 @@
       </c>
       <c r="BC73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -18364,7 +18364,7 @@
       </c>
       <c r="BC74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="BC75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -19778,9 +19778,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -20028,9 +20028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -20055,9 +20055,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -20305,9 +20305,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -20886,9 +20886,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -21136,9 +21136,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21163,9 +21163,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -21413,9 +21413,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21994,9 +21994,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -22244,9 +22244,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -22271,9 +22271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -22521,9 +22521,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -23102,9 +23102,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -23252,14 +23252,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK26" s="6" t="inlineStr">
@@ -23352,9 +23352,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -23379,9 +23379,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -23529,14 +23529,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK27" s="6" t="inlineStr">
@@ -23629,9 +23629,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -24210,9 +24210,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -24360,14 +24360,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK30" s="6" t="inlineStr">
@@ -24460,9 +24460,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -24487,9 +24487,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -24637,14 +24637,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK31" s="6" t="inlineStr">
@@ -24737,9 +24737,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -25318,9 +25318,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -25468,14 +25468,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK34" s="6" t="inlineStr">
@@ -25568,9 +25568,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -25595,9 +25595,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -25745,14 +25745,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK35" s="6" t="inlineStr">
@@ -25845,9 +25845,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -26421,14 +26421,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -26576,14 +26576,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK38" s="6" t="inlineStr">
@@ -26676,9 +26676,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC38" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -26698,14 +26698,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -26853,14 +26853,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK39" s="6" t="inlineStr">
@@ -26953,9 +26953,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC39" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -26975,14 +26975,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -27130,14 +27130,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK40" s="6" t="inlineStr">
@@ -27230,9 +27230,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC40" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -27252,14 +27252,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -27407,14 +27407,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK41" s="6" t="inlineStr">
@@ -27507,9 +27507,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC41" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -27529,14 +27529,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -27684,14 +27684,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK42" s="6" t="inlineStr">
@@ -27784,9 +27784,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -27806,14 +27806,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -27961,14 +27961,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK43" s="6" t="inlineStr">
@@ -28061,9 +28061,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC43" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -28083,14 +28083,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -28238,14 +28238,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK44" s="6" t="inlineStr">
@@ -28338,9 +28338,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -28360,14 +28360,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -28515,14 +28515,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK45" s="6" t="inlineStr">
@@ -28615,9 +28615,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC45" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -28637,14 +28637,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -28792,14 +28792,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK46" s="6" t="inlineStr">
@@ -28892,9 +28892,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BC46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -28914,14 +28914,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -29069,14 +29069,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK47" s="6" t="inlineStr">
@@ -29169,9 +29169,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -29750,9 +29750,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -29900,14 +29900,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK50" s="6" t="inlineStr">
@@ -30000,9 +30000,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC50" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -30027,9 +30027,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -30177,14 +30177,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK51" s="6" t="inlineStr">
@@ -30277,9 +30277,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC51" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC51" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -30304,9 +30304,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -30454,14 +30454,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK52" s="6" t="inlineStr">
@@ -30554,9 +30554,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC52" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -30581,9 +30581,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -30731,14 +30731,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK53" s="6" t="inlineStr">
@@ -30831,9 +30831,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC53" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -30858,9 +30858,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -31008,14 +31008,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK54" s="6" t="inlineStr">
@@ -31108,9 +31108,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC54" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -31135,9 +31135,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -31285,14 +31285,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK55" s="6" t="inlineStr">
@@ -31385,9 +31385,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC55" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -31412,9 +31412,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -31562,14 +31562,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK56" s="6" t="inlineStr">
@@ -31662,9 +31662,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC56" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -31689,9 +31689,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -31839,14 +31839,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK57" s="6" t="inlineStr">
@@ -31939,9 +31939,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC57" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -31966,9 +31966,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -32116,14 +32116,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK58" s="6" t="inlineStr">
@@ -32216,9 +32216,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC58" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -32243,9 +32243,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -32393,14 +32393,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AJ59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK59" s="6" t="inlineStr">
@@ -32493,9 +32493,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC59" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -33074,9 +33074,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -33224,14 +33224,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI62" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ62" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK62" s="6" t="inlineStr">
@@ -33324,9 +33324,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC62" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -33351,9 +33351,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -33501,14 +33501,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI63" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ63" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI63" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ63" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK63" s="6" t="inlineStr">
@@ -33601,9 +33601,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC63" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC63" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -33628,9 +33628,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -33778,14 +33778,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK64" s="6" t="inlineStr">
@@ -33878,9 +33878,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -33905,9 +33905,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -34055,14 +34055,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI65" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ65" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK65" s="6" t="inlineStr">
@@ -34155,9 +34155,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC65" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -34182,9 +34182,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -34332,14 +34332,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI66" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ66" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK66" s="6" t="inlineStr">
@@ -34432,9 +34432,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC66" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC66" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -34459,9 +34459,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -34609,14 +34609,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI67" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ67" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK67" s="6" t="inlineStr">
@@ -34709,9 +34709,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC67" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -34736,9 +34736,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -34886,14 +34886,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK68" s="6" t="inlineStr">
@@ -34986,9 +34986,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -35013,9 +35013,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -35163,14 +35163,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI69" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ69" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK69" s="6" t="inlineStr">
@@ -35263,9 +35263,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC69" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -35290,9 +35290,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -35440,14 +35440,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI70" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ70" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK70" s="6" t="inlineStr">
@@ -35540,9 +35540,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC70" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -35567,9 +35567,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -35717,14 +35717,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI71" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ71" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK71" s="6" t="inlineStr">
@@ -35817,9 +35817,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC71" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -35844,9 +35844,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -35994,14 +35994,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI72" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ72" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK72" s="6" t="inlineStr">
@@ -36094,9 +36094,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC72" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36121,9 +36121,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -36271,14 +36271,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI73" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ73" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK73" s="6" t="inlineStr">
@@ -36371,9 +36371,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC73" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36398,9 +36398,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -36548,14 +36548,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK74" s="6" t="inlineStr">
@@ -36648,9 +36648,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36675,9 +36675,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -36825,14 +36825,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AI75" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ75" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AI75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AJ75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK75" s="6" t="inlineStr">
@@ -36925,9 +36925,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC75" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC75" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36946,7 +36946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37112,7 +37112,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP151D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -37134,7 +37134,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP151D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -37156,7 +37156,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32MP153A</t>
+          <t>STM32MP151D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -37178,7 +37178,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP151F</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -37200,7 +37200,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP151F</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -37222,7 +37222,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32MP153C</t>
+          <t>STM32MP151F</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -37244,7 +37244,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32MP157A</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -37266,7 +37266,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32MP157A</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -37288,7 +37288,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32MP157A</t>
+          <t>STM32MP153A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -37310,7 +37310,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32MP157C</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -37332,7 +37332,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32MP157C</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -37354,7 +37354,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32MP157C</t>
+          <t>STM32MP153C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -37376,12 +37376,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP153D</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -37391,19 +37391,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP153D</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -37413,19 +37413,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP153D</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -37435,19 +37435,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP153F</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -37457,19 +37457,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32MP211C</t>
+          <t>STM32MP153F</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -37479,19 +37479,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32MP211C</t>
+          <t>STM32MP153F</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -37501,19 +37501,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32MP211C</t>
+          <t>STM32MP157A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -37523,19 +37523,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32MP211C</t>
+          <t>STM32MP157A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -37545,19 +37545,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32MP231A</t>
+          <t>STM32MP157A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -37567,19 +37567,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32MP231A</t>
+          <t>STM32MP157C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -37589,19 +37589,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32MP231A</t>
+          <t>STM32MP157C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -37611,19 +37611,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32MP231C</t>
+          <t>STM32MP157C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -37633,19 +37633,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32MP231C</t>
+          <t>STM32MP157D</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -37655,19 +37655,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32MP231C</t>
+          <t>STM32MP157D</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -37677,19 +37677,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32MP251A</t>
+          <t>STM32MP157D</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -37699,19 +37699,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32MP251A</t>
+          <t>STM32MP157F</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -37721,19 +37721,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32MP251A</t>
+          <t>STM32MP157F</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -37743,19 +37743,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32MP251C</t>
+          <t>STM32MP157F</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -37765,19 +37765,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32MP251C</t>
+          <t>STM32MP211A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -37787,27 +37787,2887 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>STM32MP211A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32MP211A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32MP211A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32MP211C</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32MP211C</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32MP211C</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32MP211C</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32MP211D</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32MP211D</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32MP211D</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32MP211D</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32MP211F</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32MP211F</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32MP211F</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32MP211F</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32MP213A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32MP213A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32MP213A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32MP213A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32MP213C</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32MP213C</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32MP213C</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32MP213C</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32MP213D</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32MP213D</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32MP213D</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32MP213D</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32MP213F</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32MP213F</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32MP213F</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32MP213F</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32MP215A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32MP215A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32MP215A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32MP215A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32MP215C</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32MP215C</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32MP215C</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32MP215C</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32MP215D</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32MP215D</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32MP215D</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32MP215D</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32MP215F</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32MP215F</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32MP215F</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32MP215F</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32MP231A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32MP231A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32MP231A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32MP231C</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32MP231C</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32MP231C</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32MP231D</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32MP231D</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32MP231D</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32MP231F</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32MP231F</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32MP231F</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32MP233A</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32MP233A</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32MP233A</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32MP233C</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32MP233C</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32MP233C</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32MP233D</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32MP233D</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32MP233D</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32MP233F</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32MP233F</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STM32MP233F</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32MP235A</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32MP235A</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STM32MP235A</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STM32MP235C</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>STM32MP235C</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STM32MP235C</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32MP235D</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32MP235D</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32MP235D</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32MP235F</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32MP235F</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32MP235F</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32MP251A</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32MP251A</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32MP251A</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>STM32MP251C</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32MP251C</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32MP251C</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32MP251D</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32MP251D</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32MP251D</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32MP251F</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32MP251F</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32MP251F</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32MP253A</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32MP253A</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32MP253A</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STM32MP253C</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32MP253C</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32MP253C</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32MP253D</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32MP253D</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32MP253D</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>STM32MP253F</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>STM32MP253F</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>STM32MP253F</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>STM32MP255A</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>STM32MP255A</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>STM32MP255A</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>STM32MP255C</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>STM32MP255C</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>STM32MP255C</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>STM32MP255D</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>STM32MP255D</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>STM32MP255D</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>STM32MP255F</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>STM32MP255F</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>STM32MP255F</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>STM32MP257A</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>STM32MP257A</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>STM32MP257A</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>STM32MP257C</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>STM32MP257C</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>STM32MP257C</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>STM32MP257D</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>STM32MP257D</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>STM32MP257D</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>STM32MP257F</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>STM32MP257F</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>STM32MP257F</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
         <is>
           <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32 Arm Cortex MPUs.xlsx
+++ b/product_selector_out/STM32 Arm Cortex MPUs.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC75"/>
+  <dimension ref="A1:BD75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.828125" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,8 @@
     <col width="18" customWidth="1" min="52" max="52"/>
     <col width="18" customWidth="1" min="53" max="53"/>
     <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="52" customWidth="1" min="55" max="55"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="52" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -839,6 +840,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -916,6 +922,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1190,6 +1197,11 @@
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp131a.pdf</t>
         </is>
       </c>
@@ -1467,6 +1479,11 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp131c.pdf</t>
         </is>
       </c>
@@ -1747,6 +1764,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2024,6 +2046,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2298,6 +2325,11 @@
       </c>
       <c r="BC16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp133a.pdf</t>
         </is>
       </c>
@@ -2575,6 +2607,11 @@
       </c>
       <c r="BC17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp133c.pdf</t>
         </is>
       </c>
@@ -2855,6 +2892,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3132,6 +3174,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3406,6 +3453,11 @@
       </c>
       <c r="BC20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp135a.pdf</t>
         </is>
       </c>
@@ -3683,6 +3735,11 @@
       </c>
       <c r="BC21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp135c.pdf</t>
         </is>
       </c>
@@ -3963,6 +4020,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4240,6 +4302,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4514,6 +4581,11 @@
       </c>
       <c r="BC24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp151a.pdf</t>
         </is>
       </c>
@@ -4791,6 +4863,11 @@
       </c>
       <c r="BC25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp151c.pdf</t>
         </is>
       </c>
@@ -5071,6 +5148,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5348,6 +5430,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -5622,6 +5709,11 @@
       </c>
       <c r="BC28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp153a.pdf</t>
         </is>
       </c>
@@ -5899,6 +5991,11 @@
       </c>
       <c r="BC29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp153c.pdf</t>
         </is>
       </c>
@@ -6179,6 +6276,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -6456,6 +6558,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6730,6 +6837,11 @@
       </c>
       <c r="BC32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp157a.pdf</t>
         </is>
       </c>
@@ -7007,6 +7119,11 @@
       </c>
       <c r="BC33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp157c.pdf</t>
         </is>
       </c>
@@ -7287,6 +7404,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD34" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -7564,6 +7686,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -7838,6 +7965,11 @@
       </c>
       <c r="BC36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
@@ -8115,6 +8247,11 @@
       </c>
       <c r="BC37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
@@ -8395,6 +8532,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -8672,6 +8814,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -8949,6 +9096,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -9226,6 +9378,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -9503,6 +9660,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD42" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -9780,6 +9942,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD43" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -10057,6 +10224,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -10334,6 +10506,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD45" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -10611,6 +10788,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD46" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -10888,6 +11070,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD47" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -11162,6 +11349,11 @@
       </c>
       <c r="BC48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
@@ -11439,6 +11631,11 @@
       </c>
       <c r="BC49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
@@ -11719,6 +11916,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD50" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -11996,6 +12198,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD51" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -12273,6 +12480,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD52" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -12550,6 +12762,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD53" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -12827,6 +13044,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD54" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -13104,6 +13326,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -13381,6 +13608,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD56" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -13658,6 +13890,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD57" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -13935,6 +14172,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD58" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -14212,6 +14454,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD59" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -14486,6 +14733,11 @@
       </c>
       <c r="BC60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
@@ -14763,6 +15015,11 @@
       </c>
       <c r="BC61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
@@ -15043,6 +15300,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD62" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -15320,6 +15582,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD63" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -15597,6 +15864,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD64" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -15874,6 +16146,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD65" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -16151,6 +16428,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD66" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -16428,6 +16710,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -16705,6 +16992,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD68" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -16982,6 +17274,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -17259,6 +17556,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD70" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -17536,6 +17838,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD71" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -17813,6 +18120,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD72" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -18090,6 +18402,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -18367,6 +18684,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD74" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -18644,9 +18966,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="56">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AU10:AU11"/>
@@ -18658,16 +18985,18 @@
     <mergeCell ref="AH10:AH11"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="M10:M11"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AJ10:AJ11"/>
-    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AP10:AP11"/>
-    <mergeCell ref="BA10:BA11"/>
-    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="AD10:AE10"/>
     <mergeCell ref="AF10:AG10"/>
     <mergeCell ref="AC10:AC11"/>
@@ -18681,9 +19010,8 @@
     <mergeCell ref="Z10:Z11"/>
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
-    <mergeCell ref="A1:BC8"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A9:BC9"/>
+    <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="U10:U11"/>
@@ -18780,7 +19108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC75"/>
+  <dimension ref="A1:BD75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18838,6 +19166,7 @@
     <col width="16" customWidth="1" min="53" max="53"/>
     <col width="16" customWidth="1" min="54" max="54"/>
     <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19125,6 +19454,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -19202,6 +19536,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -19474,7 +19809,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="6" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19751,7 +20091,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="6" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20033,6 +20378,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -20310,6 +20660,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -20582,7 +20937,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="6" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20859,7 +21219,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="6" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21141,6 +21506,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -21418,6 +21788,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -21690,7 +22065,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="6" t="inlineStr">
+      <c r="BC20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21967,7 +22347,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="6" t="inlineStr">
+      <c r="BC21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22249,6 +22634,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -22526,6 +22916,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -22798,7 +23193,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC24" s="6" t="inlineStr">
+      <c r="BC24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23075,7 +23475,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC25" s="6" t="inlineStr">
+      <c r="BC25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23357,6 +23762,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -23634,6 +24044,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -23906,7 +24321,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC28" s="6" t="inlineStr">
+      <c r="BC28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24183,7 +24603,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC29" s="6" t="inlineStr">
+      <c r="BC29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24465,6 +24890,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -24742,6 +25172,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -25014,7 +25449,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC32" s="6" t="inlineStr">
+      <c r="BC32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25291,7 +25731,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC33" s="6" t="inlineStr">
+      <c r="BC33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25573,6 +26018,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -25850,6 +26300,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -26122,7 +26577,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC36" s="6" t="inlineStr">
+      <c r="BC36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26399,7 +26859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC37" s="6" t="inlineStr">
+      <c r="BC37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26681,6 +27146,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -26958,6 +27428,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -27235,6 +27710,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -27512,6 +27992,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -27789,6 +28274,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -28066,6 +28556,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -28343,6 +28838,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -28620,6 +29120,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -28897,6 +29402,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -29174,6 +29684,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -29446,7 +29961,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC48" s="6" t="inlineStr">
+      <c r="BC48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29723,7 +30243,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC49" s="6" t="inlineStr">
+      <c r="BC49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30005,6 +30530,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -30282,6 +30812,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -30559,6 +31094,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -30836,6 +31376,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -31113,6 +31658,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -31390,6 +31940,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -31667,6 +32222,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -31944,6 +32504,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -32221,6 +32786,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -32498,6 +33068,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -32770,7 +33345,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC60" s="6" t="inlineStr">
+      <c r="BC60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33047,7 +33627,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC61" s="6" t="inlineStr">
+      <c r="BC61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33329,6 +33914,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -33606,6 +34196,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -33883,6 +34478,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -34160,6 +34760,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -34437,6 +35042,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -34714,6 +35324,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -34991,6 +35606,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -35268,6 +35888,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -35545,6 +36170,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -35822,6 +36452,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -36099,6 +36734,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -36376,6 +37016,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -36653,6 +37298,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -36930,11 +37580,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BC9"/>
-    <mergeCell ref="A1:BC8"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
